--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.59739720156315</v>
+        <v>3.347077045254012</v>
       </c>
       <c r="D2" t="n">
-        <v>20.50263001481528</v>
+        <v>3.331677377407484</v>
       </c>
       <c r="E2" t="n">
-        <v>5.949956885754378</v>
+        <v>0.9668679939350864</v>
       </c>
       <c r="F2" t="n">
-        <v>5.660012167095424</v>
+        <v>0.9197519771530064</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.40244260641658</v>
+        <v>2.665396923542695</v>
       </c>
       <c r="D3" t="n">
-        <v>16.61194721047045</v>
+        <v>2.699441421701448</v>
       </c>
       <c r="E3" t="n">
-        <v>5.949956885754378</v>
+        <v>0.9668679939350864</v>
       </c>
       <c r="F3" t="n">
-        <v>5.660012167095424</v>
+        <v>0.9197519771530064</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.0984946722813</v>
+        <v>5.053505384245711</v>
       </c>
       <c r="D4" t="n">
-        <v>29.44033130687679</v>
+        <v>4.784053837367479</v>
       </c>
       <c r="E4" t="n">
-        <v>5.949956885754378</v>
+        <v>0.9668679939350864</v>
       </c>
       <c r="F4" t="n">
-        <v>5.660012167095424</v>
+        <v>0.9197519771530064</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.70021506728325</v>
+        <v>2.713784948433528</v>
       </c>
       <c r="D5" t="n">
-        <v>14.73613672564803</v>
+        <v>2.394622217917804</v>
       </c>
       <c r="E5" t="n">
-        <v>5.949956885754378</v>
+        <v>0.9668679939350864</v>
       </c>
       <c r="F5" t="n">
-        <v>5.660012167095424</v>
+        <v>0.9197519771530064</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
